--- a/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-004_権限設計書.xlsx
+++ b/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-004_権限設計書.xlsx
@@ -75,7 +75,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -97,11 +97,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,6 +155,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -499,6 +533,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -507,6 +544,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -518,7 +557,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -531,7 +570,7 @@
           <t>KF-BD-004</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -541,10 +580,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -557,7 +596,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -570,8 +609,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -618,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -677,6 +718,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更（全ロール・本人のみ。API-023）を追加。アカウントロックの手動解除は未実装と明記</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -778,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1049,6 +1113,60 @@
       </c>
       <c r="E12" s="8" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>自分のパスワード変更</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>本人のみ（API-023。JWT の利用者本人のパスワードのみ変更可。他人の変更・管理者による初期化は対象外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>アカウントロックの解除</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>未実装。ロックは 30 分で自動解除（管理者による手動解除は今後の課題）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>

--- a/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-004_権限設計書.xlsx
+++ b/docs/02_基本設計/05_権限・メッセージ・帳票/KF-BD-004_権限設計書.xlsx
@@ -11,6 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ロール定義" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="機能別権限" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API別権限" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="認証・認可の仕組み" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="画面アクセス制御" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -75,7 +78,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -130,11 +133,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +165,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -580,7 +595,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="10" t="n"/>
@@ -659,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -741,6 +756,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装（SecurityConfig・@PreAuthorize・ActiveUserFilter・PasswordChangeRequiredFilter・router）と照合。機能別権限を実装に合わせて修正（部下の集計は上長のみ・管理者は不可／最終承認は管理者のみ／管理者によるパスワード再設定・ロック解除の扱い／通知・休暇残日数・申請詳細の閲覧範囲）。API別権限・認証・認可の仕組み・画面アクセス制御のシートを追加</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の打刻（API-024・025）と部署一覧（API-026）の権限を追加（いずれも認証必須・ロール制限なし。打刻は本人のみ）。休憩・離席修正申請の申請・承認の権限を既存の申請と同じ扱いで追記。管理者によるパスワード再設定が password_changed_at を更新して旧トークンを失効させる点、初期・再設定パスワードに本人変更と同じポリシーを適用する点を修正（従来は「失効しない」「8〜72 文字」）</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -792,7 +853,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>一般の利用者</t>
+          <t>一般の利用者（画面表示は「社員」）</t>
         </is>
       </c>
     </row>
@@ -809,7 +870,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>部下の申請を承認する管理職。従業員の機能も利用可</t>
+          <t>部下の申請を承認（1 段目）し、直属の部下の月次集計を閲覧する管理職。従業員の機能も利用可</t>
         </is>
       </c>
     </row>
@@ -826,7 +887,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>システム管理と最終承認。全機能を利用可</t>
+          <t>システム管理と最終承認（2 段目）。従業員の機能と管理系 API を利用可。上長用の「部下の集計」（API-020）は利用不可</t>
         </is>
       </c>
     </row>
@@ -842,23 +903,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>○：利用可　△：条件付きで利用可　×：利用不可。画面の非表示に加え、バックエンドでロールとデータ所有を必ず検証する。</t>
-        </is>
-      </c>
-    </row>
+          <t>○：利用可　△：条件付きで利用可　×：利用不可。画面の非表示に加え、バックエンドでロールとデータ所有を必ず検証する（実装：SecurityConfig・@PreAuthorize・Service）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -889,7 +951,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>自分の打刻</t>
+          <t>ログイン</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -909,14 +971,14 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>自分のデータのみ</t>
+          <t>未認証で呼べる API はログイン（API-001）と /actuator/health のみ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>打刻修正・休暇の申請</t>
+          <t>自分の打刻（出勤・退勤・休憩・離席）</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -936,14 +998,14 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>自分のデータのみ</t>
+          <t>自分のデータのみ（ロール制限なし）。休憩・離席の開始・終了（API-024・025）も本人・本日のみ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>申請の取下げ</t>
+          <t>打刻修正・休憩離席修正・休暇の申請</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -963,51 +1025,51 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>承認前の自分の申請</t>
+          <t>自分のデータのみ（打刻修正・休憩離席修正は自分の勤怠のみ対象）。申請者は常にトークンの本人（本文に userId は持たない）。下書き保存・提出・再提出</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>部下の申請の承認</t>
+          <t>自分の申請の閲覧</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>自分の承認ルートに該当する申請のみ。自分の申請は不可</t>
+          <t>一覧は自分の申請のみ（管理者も同じ）。詳細は本人・その申請の承認ステップの承認者・管理者のみ（他人の下書きは不可）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>部下の勤怠・休暇の閲覧</t>
+          <t>申請の取下げ</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>△</t>
+          <t>○</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1017,14 +1079,14 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>上長は自分の部下のみ、管理者は全員</t>
+          <t>承認前（下書き・承認待ち・差戻し）の自分の申請のみ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>ユーザー管理</t>
+          <t>申請の承認・差戻し・却下（1 段目）</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1034,20 +1096,24 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>△</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>承認ルートの 1 段目に指名された本人のみ（申請者の上長＝users.manager_id が有効なとき）。自分の申請は不可（E-009）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>休暇種別・祝日マスタ管理</t>
+          <t>最終承認（2 段目）</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1062,15 +1128,19 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>管理者のみ（有効な管理者であれば誰でも処理可。ただし自分の申請は不可）。申請者に有効な上長がいない場合は 2 段目のみ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>休暇付与管理</t>
+          <t>承認待ち一覧の参照</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -1080,20 +1150,24 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>△</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr"/>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>上長は自分が 1 段目に指名された申請のみ（休暇・打刻修正・休憩離席修正の全種別）。管理者は自分宛の 1 段目と全員分の 2 段目</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>月次集計・CSV出力</t>
+          <t>部下の勤怠・休暇の閲覧（部下の集計）</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -1103,30 +1177,34 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>△</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr"/>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>上長は直属の部下のみ（API-020）。管理者はこの API を呼べない（403）。全社の集計は「月次集計・CSV 出力」で参照</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>自分のパスワード変更</t>
+          <t>ユーザー管理</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>○</t>
+          <t>×</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1136,34 +1214,277 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>本人のみ（API-023。JWT の利用者本人のパスワードのみ変更可。他人の変更・管理者による初期化は対象外）</t>
+          <t>登録・変更・無効化・パスワード再設定（初期・再設定パスワードは本人変更と同じポリシー）。自分自身の無効化・ロール変更は不可。有効な部下がいる上長の無効化・従業員化は不可（E-016）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
+          <t>休暇種別・祝日マスタ管理</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>年次有給休暇の名称・有給区分・日数ルール・有効フラグは変更不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>休暇付与管理</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>手動付与・付与日数の調整。付与・調整時は本人へ通知</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>月次集計・CSV出力</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>全社・部署別（API-018）。CSV は RPT-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>休暇残日数の参照</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>本人のみ（他人の userId を指定する手段はない。管理者も同じ）。管理者による他人の付与履歴参照は休暇付与管理（API-017）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>有効な休暇種別の参照</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>申請画面のプルダウン用（API-021）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>部署一覧の参照</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>ユーザー管理・月次集計の部署プルダウン用（API-026 GET /api/departments）。認証必須でロールの制限なし。部署名・IDのみで個人情報を含まない</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>通知の参照・既読化</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>自分の通知のみ（他人の通知は E-010）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>自分のパスワード変更</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>本人のみ（API-023。JWT の利用者本人のパスワードのみ変更可）。要パスワード変更のトークンで呼べる唯一の API</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>他人のパスワード再設定</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>管理者のみ（PUT /api/admin/users/{id}/password）。設定後は本人が要パスワード変更となり、失敗回数・ロックも解除され、以前に発行されたトークンは失効する（再ログインが必要）。設定するパスワードは本人変更と同じポリシー（12〜72 文字・英字と数字を含む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>アカウントロックの解除</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>未実装。ロックは 30 分で自動解除（管理者による手動解除は今後の課題）</t>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>専用の解除機能は未実装。ロックは 30 分で自動解除。管理者のパスワード再設定でも解除される</t>
         </is>
       </c>
     </row>
@@ -1171,4 +1492,964 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※○：呼出し可　×：403（E-010）。未認証は 401（E-001）。要パスワード変更のトークンは API-023 以外を 403（E-019）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>上長</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>判定箇所（実装）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login（API-001）</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>permitAll</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/auth/password（API-023）</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>authenticated。PasswordChangeRequiredFilter の例外（要パスワード変更のトークンでも可）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/attendance/clock-in・clock-out・break-start・break-end、GET /api/attendance（API-002〜004, 024, 025）</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>authenticated。対象は常に JWT の本人</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>POST・GET /api/requests、GET /api/requests/{id}、POST /api/requests/{id}/withdraw・submit（API-005〜008, 022）</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>authenticated。Service で本人・承認者・管理者のデータ所有を検証（休憩・離席修正申請も同じ）（不存在と権限なしは区別せず E-010）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>GET /api/approvals/pending、POST /api/approvals/{stepId}/approve|return|reject（API-009〜012）</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>@PreAuthorize hasAnyRole(MANAGER, ADMIN)。Service が DB で ACTIVE・ロールを再確認し、1 段目は指名された本人、2 段目は ADMIN を要求。判定順は E-010 → E-009 → E-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>GET /api/leave-balances、GET /api/leave-types（API-013, 021）</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>authenticated</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>GET /api/departments（API-026）</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>authenticated（SecurityConfig の anyRequest。@PreAuthorize は付けない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>GET・POST /api/notifications、POST /api/notifications/{id}/read（API-019）</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>authenticated。本人の通知のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>GET /api/manager/subordinates/summary（API-020）</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>@PreAuthorize hasRole(MANAGER)。ADMIN も 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>/api/admin/users（API-014）、/api/admin/leave-types（API-015）、/api/admin/holidays（API-016）、/api/admin/leave-grants（API-017）、GET /api/admin/reports/monthly（API-018）</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>SecurityConfig の /api/admin/** hasRole(ADMIN) ＋ 各 Controller の @PreAuthorize hasRole(ADMIN)（多重防御）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>GET /actuator/health</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>permitAll（未認証可。health のみ公開）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>認証方式</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Bearer JWT（HS256 署名、有効 2 時間）。セッションなし（STATELESS）・CSRF 無効。トークンの role クレームを ROLE_{role} の権限に変換する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>リクエストの判定順</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>①BearerTokenAuthenticationFilter（JWT の署名・期限）→ ②ActiveUserFilter → ③PasswordChangeRequiredFilter → ④認可ルール（SecurityConfig）→ ⑤@PreAuthorize（@EnableMethodSecurity）→ ⑥Service のデータ所有検証</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>認可ルール（SecurityConfig）</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>POST /api/auth/login と GET /actuator/health(/**) は permitAll。/api/admin/** は hasRole(ADMIN)。それ以外は authenticated</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ActiveUserFilter</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>リクエストごとに users を主キー検索し、(1) 存在しない／status≠ACTIVE、(2) トークン発行（iat）がパスワード変更日時（password_changed_at）より前、のいずれかなら 401（E-001）。退職・無効化されたユーザーのトークンが期限まで使えることを防ぐ。※本人によるパスワード変更と、管理者によるパスワード再設定のどちらも password_changed_at を更新するため、それ以前に発行されたトークンは失効する</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>PasswordChangeRequiredFilter</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>トークンの mcp クレーム（must_change_password）が true のとき、/api/auth/password 以外の全 API を 403（E-019）にする。画面側のルーターガードに依存しないサーバー側の強制</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>エラー応答</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>トークンなし・不正・期限切れ→401 / E-001、権限不足→403 / E-010、いずれも共通エラー形式（JSON）。@PreAuthorize による拒否も GlobalExceptionHandler で 403 / E-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>ロールの扱い</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>JWT の role を権限チェックに使うが、承認系（ApprovalService#requireApprover）・申請（有効ユーザー確認）は DB のロール・状態を再確認する。ロール変更は既発行トークンの role クレームには反映されない（最長 2 時間）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>自己保護・整合性</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>管理者は自分自身を無効化・ロール降格できない（E-010）。有効な部下がいる上長は無効化・従業員化できない（E-016）。自分の申請は承認・差戻し・却下できない（E-009）。上長に指定できるのは有効な MANAGER / ADMIN で、循環参照は不可（E-014）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>パスワード・ロック</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>BCrypt でハッシュ化。ログイン失敗 5 回で 30 分ロック（E-017）。パスワード変更で現在のパスワードを誤った場合も失敗回数に加算する。管理者によるパスワード再設定は要変更フラグを立て、ロック・失敗回数を解除し、パスワード変更日時を更新して旧トークンを失効させる。管理者が設定する初期・再設定パスワードにも本人変更と同じポリシー（12 文字以上・英字と数字を含む）を適用する</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>未実装（今後）</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>トークンの失効（ログアウト無効化）・リフレッシュトークン、ロール変更の即時反映、監査ログ（audit_logs）、管理者によるロック解除の専用機能</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>※フロントのルーターガード（router/index.js）。未ログインは /login へ、ロール不一致は /home へリダイレクトする（権限エラー専用画面は無い）。要パスワード変更のユーザーは /password 以外へ入れず /password へ誘導する。API 側は上記のとおり別途検証する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>ルート</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>画面ID</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>従業員</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>上長</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>/login</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>未ログイン可</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>/home</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>SCR-101, 102, 103</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>/password</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>/requests、/requests/new、/requests/:id</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>SCR-104〜106, 109, 202</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>/leave</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>SCR-107</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>/notifications</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>SCR-108</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>/approvals</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>SCR-201, 301</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>/manager/summary</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>SCR-203</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>/admin/reports</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>SCR-306</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>/admin/users</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>SCR-302</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>/admin/leave-grants</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>SCR-305</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>/admin/leave-types</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>SCR-303</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>/admin/holidays</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>SCR-304</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>（上記以外の URL）</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>/home へ</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>/home へ</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>/home へ</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>